--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.42912990867816</v>
+      </c>
+      <c r="C2">
         <v>29.41018295394608</v>
-      </c>
-      <c r="C2">
-        <v>27.42912990867816</v>
       </c>
       <c r="D2">
         <v>3.400182860357984</v>
       </c>
       <c r="E2">
-        <v>18.75179278533724</v>
+        <v>17.48868278497456</v>
       </c>
       <c r="F2">
         <v>63.75952442968819</v>
       </c>
       <c r="G2">
-        <v>17.48868278497456</v>
+        <v>18.75179278533724</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.69926094371802</v>
+      </c>
+      <c r="C3">
         <v>38.84783020655676</v>
-      </c>
-      <c r="C3">
-        <v>30.69926094371802</v>
       </c>
       <c r="D3">
         <v>2.574146341463415</v>
       </c>
       <c r="E3">
-        <v>22.91270817033643</v>
+        <v>18.10662791997317</v>
       </c>
       <c r="F3">
         <v>58.9806639096904</v>
       </c>
       <c r="G3">
-        <v>18.10662791997317</v>
+        <v>22.91270817033643</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>31.0818787418838</v>
+      </c>
+      <c r="C4">
         <v>45.0543890715912</v>
-      </c>
-      <c r="C4">
-        <v>31.0818787418838</v>
       </c>
       <c r="D4">
         <v>2.219539584503088</v>
       </c>
       <c r="E4">
-        <v>25.5792799693604</v>
+        <v>17.64649559555726</v>
       </c>
       <c r="F4">
         <v>56.77422443508235</v>
       </c>
       <c r="G4">
-        <v>17.64649559555726</v>
+        <v>25.5792799693604</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>33.30905117464943</v>
+      </c>
+      <c r="C5">
         <v>33.91003460207612</v>
-      </c>
-      <c r="C5">
-        <v>33.30905117464943</v>
       </c>
       <c r="D5">
         <v>2.948979591836735</v>
       </c>
       <c r="E5">
-        <v>20.2788063602701</v>
+        <v>19.91940753648443</v>
       </c>
       <c r="F5">
         <v>59.80178610324548</v>
       </c>
       <c r="G5">
-        <v>19.91940753648443</v>
+        <v>20.2788063602701</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.26762840442731</v>
+      </c>
+      <c r="C6">
         <v>39.03121502300709</v>
-      </c>
-      <c r="C6">
-        <v>28.26762840442731</v>
       </c>
       <c r="D6">
         <v>2.562051935638044</v>
       </c>
       <c r="E6">
-        <v>23.33023601561048</v>
+        <v>16.89648764170229</v>
       </c>
       <c r="F6">
         <v>59.77327634268723</v>
       </c>
       <c r="G6">
-        <v>16.89648764170229</v>
+        <v>23.33023601561048</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>30.23466727128443</v>
+      </c>
+      <c r="C7">
         <v>34.47454937081964</v>
-      </c>
-      <c r="C7">
-        <v>30.23466727128443</v>
       </c>
       <c r="D7">
         <v>2.900690562315028</v>
       </c>
       <c r="E7">
-        <v>20.930552687728</v>
+        <v>18.35639066694198</v>
       </c>
       <c r="F7">
         <v>60.71305664533003</v>
       </c>
       <c r="G7">
-        <v>18.35639066694198</v>
+        <v>20.930552687728</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.69111086932869</v>
+      </c>
+      <c r="C8">
         <v>44.89174192144489</v>
-      </c>
-      <c r="C8">
-        <v>28.69111086932869</v>
       </c>
       <c r="D8">
         <v>2.227581192438197</v>
       </c>
       <c r="E8">
-        <v>25.86185282687727</v>
+        <v>16.5287702143663</v>
       </c>
       <c r="F8">
         <v>57.60937695875642</v>
       </c>
       <c r="G8">
-        <v>16.5287702143663</v>
+        <v>25.86185282687727</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.97074329843321</v>
+      </c>
+      <c r="C9">
         <v>30.92002673201159</v>
-      </c>
-      <c r="C9">
-        <v>31.97074329843321</v>
       </c>
       <c r="D9">
         <v>3.234149855907781</v>
       </c>
       <c r="E9">
-        <v>18.9820618603697</v>
+        <v>19.62710550908303</v>
       </c>
       <c r="F9">
         <v>61.39083263054726</v>
       </c>
       <c r="G9">
-        <v>19.62710550908303</v>
+        <v>18.9820618603697</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.016020506248</v>
+      </c>
+      <c r="C10">
         <v>39.49375200256328</v>
-      </c>
-      <c r="C10">
-        <v>30.016020506248</v>
       </c>
       <c r="D10">
         <v>2.532046081453837</v>
       </c>
       <c r="E10">
-        <v>23.29880538333586</v>
+        <v>17.70754574323302</v>
       </c>
       <c r="F10">
-        <v>58.99364887343113</v>
+        <v>58.99364887343111</v>
       </c>
       <c r="G10">
-        <v>17.70754574323303</v>
+        <v>23.29880538333585</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>32.1461824953445</v>
+      </c>
+      <c r="C11">
         <v>44.1340782122905</v>
-      </c>
-      <c r="C11">
-        <v>32.1461824953445</v>
       </c>
       <c r="D11">
         <v>2.265822784810127</v>
       </c>
       <c r="E11">
-        <v>25.03631321801136</v>
+        <v>18.23583784497557</v>
       </c>
       <c r="F11">
-        <v>56.72784893701308</v>
+        <v>56.72784893701307</v>
       </c>
       <c r="G11">
-        <v>18.23583784497557</v>
+        <v>25.03631321801135</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>31.1217447317567</v>
+      </c>
+      <c r="C12">
         <v>38.11079414741879</v>
-      </c>
-      <c r="C12">
-        <v>31.1217447317567</v>
       </c>
       <c r="D12">
         <v>2.623928528310998</v>
       </c>
       <c r="E12">
-        <v>22.51977923384356</v>
+        <v>18.38992958320872</v>
       </c>
       <c r="F12">
         <v>59.09029118294771</v>
       </c>
       <c r="G12">
-        <v>18.38992958320872</v>
+        <v>22.51977923384356</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>32.00228068105855</v>
+      </c>
+      <c r="C13">
         <v>28.20180095159451</v>
-      </c>
-      <c r="C13">
-        <v>32.00228068105855</v>
       </c>
       <c r="D13">
         <v>3.545872838817624</v>
       </c>
       <c r="E13">
-        <v>17.60367193156855</v>
+        <v>19.97594590282635</v>
       </c>
       <c r="F13">
         <v>62.42038216560509</v>
       </c>
       <c r="G13">
-        <v>19.97594590282635</v>
+        <v>17.60367193156855</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>31.23148539991536</v>
+      </c>
+      <c r="C14">
         <v>35.31527719001269</v>
-      </c>
-      <c r="C14">
-        <v>31.23148539991536</v>
       </c>
       <c r="D14">
         <v>2.831635710005992</v>
       </c>
       <c r="E14">
-        <v>21.20442129335536</v>
+        <v>18.75238216236819</v>
       </c>
       <c r="F14">
         <v>60.04319654427646</v>
       </c>
       <c r="G14">
-        <v>18.75238216236819</v>
+        <v>21.20442129335536</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.76639924492685</v>
+      </c>
+      <c r="C15">
         <v>38.3317602642756</v>
-      </c>
-      <c r="C15">
-        <v>29.76639924492685</v>
       </c>
       <c r="D15">
         <v>2.6088027085257</v>
       </c>
       <c r="E15">
-        <v>22.80320044918585</v>
+        <v>17.70774845592364</v>
       </c>
       <c r="F15">
         <v>59.48905109489051</v>
       </c>
       <c r="G15">
-        <v>17.70774845592364</v>
+        <v>22.80320044918585</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>29.20249536334514</v>
+      </c>
+      <c r="C16">
         <v>27.0738492665655</v>
-      </c>
-      <c r="C16">
-        <v>29.20249536334514</v>
       </c>
       <c r="D16">
         <v>3.693601120971509</v>
       </c>
       <c r="E16">
-        <v>17.32434254888739</v>
+        <v>18.68644639244775</v>
       </c>
       <c r="F16">
         <v>63.98921105866487</v>
       </c>
       <c r="G16">
-        <v>18.68644639244775</v>
+        <v>17.32434254888739</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>33.58021591765002</v>
+      </c>
+      <c r="C17">
         <v>42.64373587747929</v>
-      </c>
-      <c r="C17">
-        <v>33.58021591765002</v>
       </c>
       <c r="D17">
         <v>2.345010303208714</v>
       </c>
       <c r="E17">
-        <v>24.19860378971363</v>
+        <v>19.05542100014247</v>
       </c>
       <c r="F17">
         <v>56.7459752101439</v>
       </c>
       <c r="G17">
-        <v>19.05542100014247</v>
+        <v>24.19860378971363</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>30.47814910025707</v>
+      </c>
+      <c r="C18">
         <v>43.19794344473008</v>
-      </c>
-      <c r="C18">
-        <v>30.47814910025707</v>
       </c>
       <c r="D18">
         <v>2.314925017852892</v>
       </c>
       <c r="E18">
-        <v>24.87270574304322</v>
+        <v>17.54884547069272</v>
       </c>
       <c r="F18">
         <v>57.57844878626406</v>
       </c>
       <c r="G18">
-        <v>17.54884547069272</v>
+        <v>24.87270574304322</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.24469413233458</v>
+      </c>
+      <c r="C19">
         <v>41.24531835205993</v>
-      </c>
-      <c r="C19">
-        <v>29.24469413233458</v>
       </c>
       <c r="D19">
         <v>2.424517593643587</v>
       </c>
       <c r="E19">
-        <v>24.19221967963386</v>
+        <v>17.1533180778032</v>
       </c>
       <c r="F19">
         <v>58.65446224256292</v>
       </c>
       <c r="G19">
-        <v>17.1533180778032</v>
+        <v>24.19221967963386</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>30.62203274876465</v>
+      </c>
+      <c r="C20">
         <v>30.14242805929658</v>
-      </c>
-      <c r="C20">
-        <v>30.62203274876465</v>
       </c>
       <c r="D20">
         <v>3.317582770813243</v>
       </c>
       <c r="E20">
-        <v>18.7494349856863</v>
+        <v>19.04776254331777</v>
       </c>
       <c r="F20">
-        <v>62.20280247099593</v>
+        <v>62.20280247099594</v>
       </c>
       <c r="G20">
-        <v>19.04776254331776</v>
+        <v>18.74943498568631</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>31.85410469298051</v>
+      </c>
+      <c r="C21">
         <v>32.16489810416019</v>
-      </c>
-      <c r="C21">
-        <v>31.85410469298051</v>
       </c>
       <c r="D21">
         <v>3.108979225619435</v>
       </c>
       <c r="E21">
-        <v>19.61047046721889</v>
+        <v>19.42098424557414</v>
       </c>
       <c r="F21">
         <v>60.96854528720697</v>
       </c>
       <c r="G21">
-        <v>19.42098424557414</v>
+        <v>19.61047046721889</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>34.98421947074532</v>
+      </c>
+      <c r="C22">
         <v>33.16338917212916</v>
-      </c>
-      <c r="C22">
-        <v>34.98421947074532</v>
       </c>
       <c r="D22">
         <v>3.015373352855051</v>
       </c>
       <c r="E22">
-        <v>19.72278371354317</v>
+        <v>20.80565983251516</v>
       </c>
       <c r="F22">
         <v>59.47155645394167</v>
       </c>
       <c r="G22">
-        <v>20.80565983251516</v>
+        <v>19.72278371354317</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>29.73796806398389</v>
+      </c>
+      <c r="C23">
         <v>34.60946894488101</v>
-      </c>
-      <c r="C23">
-        <v>29.73796806398389</v>
       </c>
       <c r="D23">
         <v>2.889382676147382</v>
       </c>
       <c r="E23">
-        <v>21.05872143477004</v>
+        <v>18.0945736697919</v>
       </c>
       <c r="F23">
         <v>60.84670489543807</v>
       </c>
       <c r="G23">
-        <v>18.0945736697919</v>
+        <v>21.05872143477004</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>31.09418694591539</v>
+      </c>
+      <c r="C24">
         <v>33.54554649848278</v>
-      </c>
-      <c r="C24">
-        <v>31.09418694591539</v>
       </c>
       <c r="D24">
         <v>2.981021638879035</v>
       </c>
       <c r="E24">
-        <v>20.37512196884825</v>
+        <v>18.8861985472155</v>
       </c>
       <c r="F24">
         <v>60.73867948393625</v>
       </c>
       <c r="G24">
-        <v>18.8861985472155</v>
+        <v>20.37512196884825</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.17581489613241</v>
+      </c>
+      <c r="C25">
         <v>43.57372065529471</v>
-      </c>
-      <c r="C25">
-        <v>29.17581489613241</v>
       </c>
       <c r="D25">
         <v>2.294961240310077</v>
       </c>
       <c r="E25">
-        <v>25.22363982988708</v>
+        <v>16.88908442098059</v>
       </c>
       <c r="F25">
         <v>57.88727574913232</v>
       </c>
       <c r="G25">
-        <v>16.88908442098059</v>
+        <v>25.22363982988708</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>39.80618028890108</v>
+      </c>
+      <c r="C26">
         <v>32.63850795392211</v>
-      </c>
-      <c r="C26">
-        <v>39.80618028890108</v>
       </c>
       <c r="D26">
         <v>3.063865546218488</v>
       </c>
       <c r="E26">
-        <v>18.92694306012088</v>
+        <v>23.08344820273566</v>
       </c>
       <c r="F26">
         <v>57.98960873714346</v>
       </c>
       <c r="G26">
-        <v>23.08344820273566</v>
+        <v>18.92694306012088</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>34.3043417949785</v>
+      </c>
+      <c r="C27">
         <v>34.27659869607435</v>
-      </c>
-      <c r="C27">
-        <v>34.3043417949785</v>
       </c>
       <c r="D27">
         <v>2.917442331040065</v>
       </c>
       <c r="E27">
-        <v>20.33242820702707</v>
+        <v>20.3488850489591</v>
       </c>
       <c r="F27">
         <v>59.31868674401382</v>
       </c>
       <c r="G27">
-        <v>20.3488850489591</v>
+        <v>20.33242820702707</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>30.65852594853903</v>
+      </c>
+      <c r="C28">
         <v>39.48975141735718</v>
-      </c>
-      <c r="C28">
-        <v>30.65852594853903</v>
       </c>
       <c r="D28">
         <v>2.532302595251243</v>
       </c>
       <c r="E28">
-        <v>23.20902217095989</v>
+        <v>18.01871075227477</v>
       </c>
       <c r="F28">
         <v>58.77226707676535</v>
       </c>
       <c r="G28">
-        <v>18.01871075227477</v>
+        <v>23.20902217095989</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.08635578583765</v>
+      </c>
+      <c r="C29">
         <v>37.56476683937824</v>
-      </c>
-      <c r="C29">
-        <v>30.08635578583765</v>
       </c>
       <c r="D29">
         <v>2.662068965517241</v>
       </c>
       <c r="E29">
+        <v>17.94581230040177</v>
+      </c>
+      <c r="F29">
+        <v>59.64767693417123</v>
+      </c>
+      <c r="G29">
         <v>22.40651076542701</v>
-      </c>
-      <c r="F29">
-        <v>59.64767693417122</v>
-      </c>
-      <c r="G29">
-        <v>17.94581230040177</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>31.48608349900596</v>
+      </c>
+      <c r="C30">
         <v>39.02833001988071</v>
-      </c>
-      <c r="C30">
-        <v>31.48608349900596</v>
       </c>
       <c r="D30">
         <v>2.562241324418975</v>
       </c>
       <c r="E30">
-        <v>22.88858121402026</v>
+        <v>18.46535014209721</v>
       </c>
       <c r="F30">
         <v>58.64606864388254</v>
       </c>
       <c r="G30">
-        <v>18.46535014209721</v>
+        <v>22.88858121402026</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.26414847732322</v>
+      </c>
+      <c r="C31">
         <v>31.49915043785126</v>
-      </c>
-      <c r="C31">
-        <v>29.26414847732322</v>
       </c>
       <c r="D31">
         <v>3.174688796680498</v>
       </c>
       <c r="E31">
-        <v>19.59349593495935</v>
+        <v>18.20325203252033</v>
       </c>
       <c r="F31">
         <v>62.20325203252033</v>
       </c>
       <c r="G31">
-        <v>18.20325203252033</v>
+        <v>19.59349593495935</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.7751577548987</v>
+      </c>
+      <c r="C32">
         <v>42.61042842909333</v>
-      </c>
-      <c r="C32">
-        <v>31.7751577548987</v>
       </c>
       <c r="D32">
         <v>2.346843335931411</v>
       </c>
       <c r="E32">
-        <v>24.43460458029805</v>
+        <v>18.22120649431033</v>
       </c>
       <c r="F32">
         <v>57.34418892539161</v>
       </c>
       <c r="G32">
-        <v>18.22120649431033</v>
+        <v>24.43460458029805</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>29.83200786346171</v>
+      </c>
+      <c r="C33">
         <v>37.84737735680458</v>
-      </c>
-      <c r="C33">
-        <v>29.83200786346171</v>
       </c>
       <c r="D33">
         <v>2.642191004603943</v>
       </c>
       <c r="E33">
-        <v>22.57127631228351</v>
+        <v>17.79110045297096</v>
       </c>
       <c r="F33">
         <v>59.63762323474554</v>
       </c>
       <c r="G33">
-        <v>17.79110045297096</v>
+        <v>22.57127631228351</v>
       </c>
     </row>
   </sheetData>
